--- a/data/trans_orig/P36BPD02_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023</t>
+          <t>Población según la cantidad de aceite de oliva que consumen al día en 2023 (tasa de respuesta: 96,13%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61806</t>
+          <t>61051</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90220</t>
+          <t>88464</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117550</t>
+          <t>118240</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148636</t>
+          <t>148849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186272</t>
+          <t>186647</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227603</t>
+          <t>227547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>19,1%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>190955</t>
+          <t>188533</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>229572</t>
+          <t>228730</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>331798</t>
+          <t>329232</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371782</t>
+          <t>371056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531575</t>
+          <t>534324</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589223</t>
+          <t>594499</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,91%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>178081</t>
+          <t>177499</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>217899</t>
+          <t>217542</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>207791</t>
+          <t>210598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>247555</t>
+          <t>248538</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,94%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>398448</t>
+          <t>395074</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>453527</t>
+          <t>451213</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>178791</t>
+          <t>184638</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327263</t>
+          <t>330254</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>210256</t>
+          <t>207032</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>329944</t>
+          <t>326139</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>440593</t>
+          <t>443851</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>634363</t>
+          <t>633473</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>618630</t>
+          <t>595703</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1024260</t>
+          <t>1028414</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>644585</t>
+          <t>639572</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>999433</t>
+          <t>994247</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1420909</t>
+          <t>1437845</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1971471</t>
+          <t>1982551</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,81%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>830448</t>
+          <t>824265</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1339087</t>
+          <t>1386440</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>856484</t>
+          <t>854060</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1314649</t>
+          <t>1313658</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,81%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1731761</t>
+          <t>1731046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2459964</t>
+          <t>2449705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,84%</t>
+          <t>56,6%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>71201</t>
+          <t>70221</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116984</t>
+          <t>119249</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64131</t>
+          <t>65102</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>94356</t>
+          <t>98608</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145797</t>
+          <t>145551</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>201288</t>
+          <t>202091</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,76%</t>
+          <t>15,82%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>280010</t>
+          <t>275637</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>330534</t>
+          <t>333314</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>44,36%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>284407</t>
+          <t>286475</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>331167</t>
+          <t>331822</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>580270</t>
+          <t>576202</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>648550</t>
+          <t>646608</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,62%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>210320</t>
+          <t>211592</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262961</t>
+          <t>264037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234627</t>
+          <t>234755</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>279441</t>
+          <t>277936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459561</t>
+          <t>460868</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>527819</t>
+          <t>529326</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>41,44%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>333789</t>
+          <t>339512</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>502115</t>
+          <t>500115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>395319</t>
+          <t>396798</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>545787</t>
+          <t>542682</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>792595</t>
+          <t>804131</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1014058</t>
+          <t>1019206</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1065038</t>
+          <t>1073451</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1550269</t>
+          <t>1544897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1169978</t>
+          <t>1241501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1653344</t>
+          <t>1659854</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2559513</t>
+          <t>2505206</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3166193</t>
+          <t>3153762</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>46,4%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1254059</t>
+          <t>1255030</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1886613</t>
+          <t>1873628</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,3%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1338257</t>
+          <t>1333909</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1970652</t>
+          <t>1890707</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>53,72%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2652378</t>
+          <t>2647851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3455257</t>
+          <t>3482029</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD02_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD02_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>73779</t>
+          <t>91195</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61051</t>
+          <t>77020</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88464</t>
+          <t>109380</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>132212</t>
+          <t>149519</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>118240</t>
+          <t>133451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148849</t>
+          <t>167250</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>205991</t>
+          <t>240714</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>186647</t>
+          <t>219177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>227547</t>
+          <t>266856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>20,42%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>209532</t>
+          <t>233961</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>188533</t>
+          <t>212638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>228730</t>
+          <t>256178</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>44,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>351382</t>
+          <t>385383</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>329232</t>
+          <t>364094</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>371056</t>
+          <t>407131</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>560914</t>
+          <t>619345</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534324</t>
+          <t>589626</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594499</t>
+          <t>649095</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,68%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>196611</t>
+          <t>206214</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>177499</t>
+          <t>185571</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>217542</t>
+          <t>228936</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>227644</t>
+          <t>240256</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>210598</t>
+          <t>220980</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>248538</t>
+          <t>259277</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>424256</t>
+          <t>446470</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>395074</t>
+          <t>418721</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>451213</t>
+          <t>478334</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>36,61%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>479923</t>
+          <t>531370</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>479923</t>
+          <t>531370</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>479923</t>
+          <t>531370</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>711239</t>
+          <t>775158</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>711239</t>
+          <t>775158</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>711239</t>
+          <t>775158</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1191161</t>
+          <t>1306528</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1191161</t>
+          <t>1306528</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1191161</t>
+          <t>1306528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>277217</t>
+          <t>335762</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184638</t>
+          <t>299228</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>330254</t>
+          <t>373982</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>279097</t>
+          <t>329994</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>207032</t>
+          <t>299551</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>326139</t>
+          <t>364909</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>556315</t>
+          <t>665755</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>443851</t>
+          <t>618712</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>633473</t>
+          <t>718324</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>17,16%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>896268</t>
+          <t>971185</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>595703</t>
+          <t>922610</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1028414</t>
+          <t>1019539</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>869900</t>
+          <t>947194</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>639572</t>
+          <t>904960</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>994247</t>
+          <t>989452</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1766168</t>
+          <t>1918378</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1437845</t>
+          <t>1855220</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1982551</t>
+          <t>1987353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>33,22%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>47,47%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>992268</t>
+          <t>794251</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>824265</t>
+          <t>746952</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1386440</t>
+          <t>840681</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1013053</t>
+          <t>808176</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>854060</t>
+          <t>766994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1313658</t>
+          <t>845600</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>38,75%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2005321</t>
+          <t>1602427</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1731046</t>
+          <t>1533923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2449705</t>
+          <t>1663261</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,34%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>39,73%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2165753</t>
+          <t>2101197</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2165753</t>
+          <t>2101197</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2165753</t>
+          <t>2101197</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2162050</t>
+          <t>2085363</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2162050</t>
+          <t>2085363</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2162050</t>
+          <t>2085363</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4327803</t>
+          <t>4186560</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4327803</t>
+          <t>4186560</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>4327803</t>
+          <t>4186560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>88884</t>
+          <t>97508</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>70221</t>
+          <t>78909</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>119249</t>
+          <t>118380</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80431</t>
+          <t>94488</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65102</t>
+          <t>78973</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>98608</t>
+          <t>113000</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>169315</t>
+          <t>191995</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>145551</t>
+          <t>167580</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>202091</t>
+          <t>219994</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,56%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>304614</t>
+          <t>336758</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>275637</t>
+          <t>305839</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>333314</t>
+          <t>364632</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,26%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>52,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>308724</t>
+          <t>344517</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>286475</t>
+          <t>317413</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>331822</t>
+          <t>365653</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,32%</t>
+          <t>44,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>613338</t>
+          <t>681276</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>576202</t>
+          <t>643467</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>646608</t>
+          <t>716847</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,7%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>237671</t>
+          <t>259973</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>211592</t>
+          <t>232835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264037</t>
+          <t>289204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>257159</t>
+          <t>280606</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>234755</t>
+          <t>258244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277936</t>
+          <t>304936</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>494831</t>
+          <t>540580</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>460868</t>
+          <t>503811</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>529326</t>
+          <t>576016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,74%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>631169</t>
+          <t>694239</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>631169</t>
+          <t>694239</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>631169</t>
+          <t>694239</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>646314</t>
+          <t>719611</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>646314</t>
+          <t>719611</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>646314</t>
+          <t>719611</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1277483</t>
+          <t>1413851</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1277483</t>
+          <t>1413851</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1277483</t>
+          <t>1413851</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>439881</t>
+          <t>524464</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>339512</t>
+          <t>480495</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>500115</t>
+          <t>576883</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>491740</t>
+          <t>574000</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>396798</t>
+          <t>534697</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>542682</t>
+          <t>617025</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>931621</t>
+          <t>1098464</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>804131</t>
+          <t>1037611</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1019206</t>
+          <t>1158764</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>16,78%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1410414</t>
+          <t>1541904</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1073451</t>
+          <t>1478910</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1544897</t>
+          <t>1605611</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>48,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1530006</t>
+          <t>1677094</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1241501</t>
+          <t>1625422</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1659854</t>
+          <t>1729549</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>47,16%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>2940420</t>
+          <t>3218998</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2505206</t>
+          <t>3136708</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>3153762</t>
+          <t>3296259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,4%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1426551</t>
+          <t>1260439</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1255030</t>
+          <t>1204745</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1873628</t>
+          <t>1325366</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>57,18%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1497857</t>
+          <t>1329038</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1333909</t>
+          <t>1283230</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1890707</t>
+          <t>1380476</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2924407</t>
+          <t>2589476</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2647851</t>
+          <t>2514618</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>3482029</t>
+          <t>2670190</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3276845</t>
+          <t>3326806</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3276845</t>
+          <t>3326806</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3276845</t>
+          <t>3326806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3519603</t>
+          <t>3580132</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3519603</t>
+          <t>3580132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3519603</t>
+          <t>3580132</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>6796448</t>
+          <t>6906938</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6796448</t>
+          <t>6906938</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6796448</t>
+          <t>6906938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
